--- a/Kiểm thử chức năng..xlsx
+++ b/Kiểm thử chức năng..xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Doan4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F090CD2-FF8F-435A-8A44-509DA8F26088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900957E1-F990-463D-9934-5342CA542577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Đăng Ký" sheetId="1" r:id="rId1"/>
     <sheet name="Đăng nhập" sheetId="4" r:id="rId2"/>
     <sheet name="Tìm kiếm " sheetId="2" r:id="rId3"/>
     <sheet name="Thông tin tài khoản" sheetId="9" r:id="rId4"/>
-    <sheet name="Báo cáo tổng kết " sheetId="10" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId5"/>
+    <sheet name="Báo cáo tổng kết " sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="386">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -1107,9 +1108,6 @@
     <t>ĐK tên TK có ký tự đặc biệt</t>
   </si>
   <si>
-    <t>Kiểm tra khi người dùng đăng ký với tên tài khoản có chứa ký tự đặc biệt (tên bị giới hạn ký tự).</t>
-  </si>
-  <si>
     <t>1. Nhập tên tài khoản: ban@!
 2. Nhập email: hoanghang@gmai.com
 3. Nhập mật khẩu: kimmh10@A1
@@ -1119,9 +1117,6 @@
     <t>Hiển thị lỗi: "Lỗi: Tên tài khoản không được gồm ký tự Đặc biệt."</t>
   </si>
   <si>
-    <t>Hệ thống hiển thị lỗi: "Lỗi: Vui lòng cung cấp tên đăng nhập hợp lệ." (Giả định rằng Vui lòng cung cấp tên đăng nhập hợp lệ là kết quả thực tế tương đương)</t>
-  </si>
-  <si>
     <t>ĐK Mật khẩu Rất yếu</t>
   </si>
   <si>
@@ -1334,19 +1329,152 @@
     <t>Các bước thực hiện</t>
   </si>
   <si>
+    <t>Hệ thống hiển thị lỗi: "Lỗi: Vui lòng cung cấp tên đăng nhập hợp lệ."</t>
+  </si>
+  <si>
+    <t>Lỗi: Tên tài khoản không được gồm ký tự Đặc biệt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiểm tra khi người dùng đăng ký với tên tài khoản có chứa ký tự đặc biệt </t>
+  </si>
+  <si>
     <t>Hệ thống hiển thị thông báo lỗi:"
-Mật khâu mới không chính xác".</t>
-  </si>
-  <si>
-    <t>Hệ thống hiển thị thông báo lỗi:"
-Mật khẩu mới không chính xác".</t>
+Vui lòng nhập mật khẩu hiện tại của bạn."</t>
+  </si>
+  <si>
+    <t>Hệ thống hiển thị thông báo lỗi:
+“Mật khâu mới không chính xác.”</t>
+  </si>
+  <si>
+    <t>tukhoa</t>
+  </si>
+  <si>
+    <t>tensp</t>
+  </si>
+  <si>
+    <t>ten</t>
+  </si>
+  <si>
+    <t>diachi</t>
+  </si>
+  <si>
+    <t>thanhpho</t>
+  </si>
+  <si>
+    <t>sdt</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>ghichu</t>
+  </si>
+  <si>
+    <t>ketquamongdoi</t>
+  </si>
+  <si>
+    <t>trơn nâu</t>
+  </si>
+  <si>
+    <t>Ly Giấy Nâu Trơn 16oz</t>
+  </si>
+  <si>
+    <t>nam</t>
+  </si>
+  <si>
+    <t>Hà Nội</t>
+  </si>
+  <si>
+    <t>0122336523</t>
+  </si>
+  <si>
+    <t>nguyennam@gmail.com</t>
+  </si>
+  <si>
+    <t>không</t>
+  </si>
+  <si>
+    <t>Mục Địa chỉ là mục bắt buộc.</t>
+  </si>
+  <si>
+    <t>Mục Tên là mục bắt buộc.</t>
+  </si>
+  <si>
+    <t>vĩnh tuy</t>
+  </si>
+  <si>
+    <t>0122336524</t>
+  </si>
+  <si>
+    <t>0122336525</t>
+  </si>
+  <si>
+    <t>0122336527</t>
+  </si>
+  <si>
+    <t>0122336528</t>
+  </si>
+  <si>
+    <t>0122336529</t>
+  </si>
+  <si>
+    <t>Mục Thị trấn / Thành phố là mục bắt buộc.</t>
+  </si>
+  <si>
+    <t>Mục Số điện thoại là mục bắt buộc.</t>
+  </si>
+  <si>
+    <t>Mục Địa chỉ email là mục bắt buộc.</t>
+  </si>
+  <si>
+    <t>Cảm ơn bạn. Đơn hàng của bạn đã được nhận.</t>
+  </si>
+  <si>
+    <t>Mục Tên là mục bắt buộc.
+Mục Địa chỉ là mục bắt buộc.</t>
+  </si>
+  <si>
+    <t>nguyennam</t>
+  </si>
+  <si>
+    <t>Mục Địa chỉ email không phải là địa chỉ email hợp lệ.</t>
+  </si>
+  <si>
+    <t>0122336530</t>
+  </si>
+  <si>
+    <t>nguyennam@@gmail.com</t>
+  </si>
+  <si>
+    <t>lieuly@gmail.com2</t>
+  </si>
+  <si>
+    <t>lieuly@gmail.com3</t>
+  </si>
+  <si>
+    <t>Emai sai</t>
+  </si>
+  <si>
+    <t>Sai định dạng email</t>
+  </si>
+  <si>
+    <t>Xin chào van (không phải van? Đăng xuất)</t>
+  </si>
+  <si>
+    <t>1. Nhập tên tài khoản: vân
+2. Nhập email: vannguyen@gmail.com31
+3. Nhập mật khẩu: thuyduyen22
+4. Nhấn "Đăng ký"</t>
+  </si>
+  <si>
+    <t>TC-DK15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1458,13 +1586,6 @@
     <font>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1473,6 +1594,20 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1856,11 +1991,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -2021,18 +2157,26 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2054,15 +2198,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Sheet1" xfId="1" xr:uid="{6EF5C705-D68B-4323-9104-7B3EB48FFC04}"/>
   </cellStyles>
@@ -2364,8 +2502,8 @@
       <c r="K1"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="E2" s="70"/>
-      <c r="F2" s="71"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="75"/>
       <c r="G2" s="4"/>
       <c r="K2"/>
     </row>
@@ -2374,10 +2512,10 @@
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="69"/>
+      <c r="F3" s="73"/>
       <c r="G3" s="17" t="s">
         <v>2</v>
       </c>
@@ -2391,10 +2529,10 @@
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
       <c r="D4" s="16"/>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="69"/>
+      <c r="F4" s="73"/>
       <c r="G4" s="17" t="s">
         <v>4</v>
       </c>
@@ -2408,10 +2546,10 @@
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="69"/>
+      <c r="F5" s="73"/>
       <c r="G5" s="18">
         <v>45516</v>
       </c>
@@ -2425,10 +2563,10 @@
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="69"/>
+      <c r="F6" s="73"/>
       <c r="G6" s="18">
         <v>41985</v>
       </c>
@@ -2442,10 +2580,10 @@
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
-      <c r="E7" s="68" t="s">
+      <c r="E7" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="69"/>
+      <c r="F7" s="73"/>
       <c r="G7" s="17"/>
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
@@ -2462,7 +2600,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
@@ -2479,7 +2617,7 @@
         <v>9</v>
       </c>
       <c r="G9" s="19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
@@ -2542,217 +2680,217 @@
       <c r="N11" s="25"/>
     </row>
     <row r="12" spans="1:14" ht="67.8" thickBot="1">
-      <c r="A12" s="63" t="s">
+      <c r="A12" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="62" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="62" t="s">
         <v>255</v>
       </c>
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="63" t="s">
+      <c r="E12" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="F12" s="63" t="s">
+      <c r="F12" s="62" t="s">
         <v>257</v>
       </c>
-      <c r="G12" s="63" t="s">
+      <c r="G12" s="62" t="s">
         <v>258</v>
       </c>
-      <c r="H12" s="63" t="s">
+      <c r="H12" s="62" t="s">
         <v>21</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" ht="67.8" thickBot="1">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="63" t="s">
+      <c r="B13" s="62" t="s">
         <v>259</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="62" t="s">
         <v>260</v>
       </c>
-      <c r="D13" s="63" t="s">
+      <c r="D13" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="63" t="s">
+      <c r="E13" s="62" t="s">
+        <v>319</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>261</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>262</v>
+      </c>
+      <c r="H13" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13"/>
+    </row>
+    <row r="14" spans="1:14" ht="67.8" thickBot="1">
+      <c r="A14" s="62" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="62" t="s">
+        <v>263</v>
+      </c>
+      <c r="C14" s="62" t="s">
+        <v>264</v>
+      </c>
+      <c r="D14" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="62" t="s">
+        <v>320</v>
+      </c>
+      <c r="F14" s="62" t="s">
+        <v>265</v>
+      </c>
+      <c r="G14" s="62" t="s">
+        <v>262</v>
+      </c>
+      <c r="H14" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14"/>
+    </row>
+    <row r="15" spans="1:14" ht="67.8" thickBot="1">
+      <c r="A15" s="62" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="62" t="s">
+        <v>266</v>
+      </c>
+      <c r="C15" s="62" t="s">
+        <v>267</v>
+      </c>
+      <c r="D15" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="62" t="s">
+        <v>268</v>
+      </c>
+      <c r="F15" s="62" t="s">
+        <v>269</v>
+      </c>
+      <c r="G15" s="62" t="s">
+        <v>262</v>
+      </c>
+      <c r="H15" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15"/>
+    </row>
+    <row r="16" spans="1:14" ht="84.6" thickBot="1">
+      <c r="A16" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="62" t="s">
+        <v>270</v>
+      </c>
+      <c r="C16" s="62" t="s">
+        <v>271</v>
+      </c>
+      <c r="D16" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="62" t="s">
         <v>321</v>
       </c>
-      <c r="F13" s="63" t="s">
-        <v>261</v>
-      </c>
-      <c r="G13" s="63" t="s">
-        <v>262</v>
-      </c>
-      <c r="H13" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13"/>
-    </row>
-    <row r="14" spans="1:14" ht="67.8" thickBot="1">
-      <c r="A14" s="63" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="63" t="s">
-        <v>263</v>
-      </c>
-      <c r="C14" s="63" t="s">
-        <v>264</v>
-      </c>
-      <c r="D14" s="63" t="s">
+      <c r="F16" s="62" t="s">
+        <v>272</v>
+      </c>
+      <c r="G16" s="62" t="s">
+        <v>273</v>
+      </c>
+      <c r="H16" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16"/>
+    </row>
+    <row r="17" spans="1:11" ht="67.8" thickBot="1">
+      <c r="A17" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="62" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" s="62" t="s">
+        <v>275</v>
+      </c>
+      <c r="D17" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="63" t="s">
-        <v>322</v>
-      </c>
-      <c r="F14" s="63" t="s">
-        <v>265</v>
-      </c>
-      <c r="G14" s="63" t="s">
-        <v>262</v>
-      </c>
-      <c r="H14" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14"/>
-    </row>
-    <row r="15" spans="1:14" ht="67.8" thickBot="1">
-      <c r="A15" s="63" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="63" t="s">
-        <v>266</v>
-      </c>
-      <c r="C15" s="63" t="s">
-        <v>267</v>
-      </c>
-      <c r="D15" s="63" t="s">
+      <c r="E17" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="F17" s="62" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="H17" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17"/>
+    </row>
+    <row r="18" spans="1:11" ht="126.6" customHeight="1" thickBot="1">
+      <c r="A18" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="C18" s="62" t="s">
+        <v>343</v>
+      </c>
+      <c r="D18" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="63" t="s">
-        <v>268</v>
-      </c>
-      <c r="F15" s="63" t="s">
-        <v>269</v>
-      </c>
-      <c r="G15" s="63" t="s">
-        <v>262</v>
-      </c>
-      <c r="H15" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15"/>
-    </row>
-    <row r="16" spans="1:14" ht="84.6" thickBot="1">
-      <c r="A16" s="63" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="63" t="s">
-        <v>270</v>
-      </c>
-      <c r="C16" s="63" t="s">
-        <v>271</v>
-      </c>
-      <c r="D16" s="63" t="s">
+      <c r="E18" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="F18" s="62" t="s">
+        <v>342</v>
+      </c>
+      <c r="G18" s="62" t="s">
+        <v>341</v>
+      </c>
+      <c r="H18" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18"/>
+    </row>
+    <row r="19" spans="1:11" ht="133.19999999999999" customHeight="1" thickBot="1">
+      <c r="A19" s="62" t="s">
+        <v>312</v>
+      </c>
+      <c r="B19" s="62" t="s">
+        <v>282</v>
+      </c>
+      <c r="C19" s="62" t="s">
+        <v>283</v>
+      </c>
+      <c r="D19" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="63" t="s">
-        <v>323</v>
-      </c>
-      <c r="F16" s="63" t="s">
-        <v>272</v>
-      </c>
-      <c r="G16" s="63" t="s">
-        <v>273</v>
-      </c>
-      <c r="H16" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16"/>
-    </row>
-    <row r="17" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A17" s="63" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="63" t="s">
-        <v>274</v>
-      </c>
-      <c r="C17" s="63" t="s">
-        <v>275</v>
-      </c>
-      <c r="D17" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" s="63" t="s">
-        <v>276</v>
-      </c>
-      <c r="F17" s="63" t="s">
-        <v>277</v>
-      </c>
-      <c r="G17" s="63" t="s">
-        <v>278</v>
-      </c>
-      <c r="H17" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17"/>
-    </row>
-    <row r="18" spans="1:11" ht="126.6" customHeight="1" thickBot="1">
-      <c r="A18" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="63" t="s">
-        <v>279</v>
-      </c>
-      <c r="C18" s="63" t="s">
-        <v>280</v>
-      </c>
-      <c r="D18" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="63" t="s">
-        <v>281</v>
-      </c>
-      <c r="F18" s="63" t="s">
-        <v>282</v>
-      </c>
-      <c r="G18" s="63" t="s">
-        <v>283</v>
-      </c>
-      <c r="H18" s="63" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18"/>
-    </row>
-    <row r="19" spans="1:11" ht="133.19999999999999" customHeight="1" thickBot="1">
-      <c r="A19" s="63" t="s">
-        <v>314</v>
-      </c>
-      <c r="B19" s="63" t="s">
+      <c r="E19" s="62" t="s">
         <v>284</v>
       </c>
-      <c r="C19" s="63" t="s">
+      <c r="F19" s="62" t="s">
         <v>285</v>
       </c>
-      <c r="D19" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="F19" s="63" t="s">
-        <v>287</v>
-      </c>
-      <c r="G19" s="63" t="s">
-        <v>287</v>
-      </c>
-      <c r="H19" s="63" t="s">
+      <c r="G19" s="62" t="s">
+        <v>285</v>
+      </c>
+      <c r="H19" s="62" t="s">
         <v>21</v>
       </c>
       <c r="I19" s="16"/>
@@ -2760,176 +2898,192 @@
       <c r="K19" s="16"/>
     </row>
     <row r="20" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A20" s="63" t="s">
+      <c r="A20" s="62" t="s">
+        <v>313</v>
+      </c>
+      <c r="B20" s="62" t="s">
+        <v>286</v>
+      </c>
+      <c r="C20" s="62" t="s">
+        <v>287</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="62" t="s">
+        <v>288</v>
+      </c>
+      <c r="F20" s="62" t="s">
+        <v>289</v>
+      </c>
+      <c r="G20" s="62" t="s">
+        <v>289</v>
+      </c>
+      <c r="H20" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20"/>
+    </row>
+    <row r="21" spans="1:11" ht="67.8" thickBot="1">
+      <c r="A21" s="62" t="s">
+        <v>314</v>
+      </c>
+      <c r="B21" s="62" t="s">
+        <v>290</v>
+      </c>
+      <c r="C21" s="62" t="s">
+        <v>291</v>
+      </c>
+      <c r="D21" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="62" t="s">
+        <v>292</v>
+      </c>
+      <c r="F21" s="62" t="s">
+        <v>281</v>
+      </c>
+      <c r="G21" s="62" t="s">
+        <v>293</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21"/>
+    </row>
+    <row r="22" spans="1:11" ht="67.8" thickBot="1">
+      <c r="A22" s="62" t="s">
         <v>315</v>
       </c>
-      <c r="B20" s="63" t="s">
-        <v>288</v>
-      </c>
-      <c r="C20" s="63" t="s">
-        <v>289</v>
-      </c>
-      <c r="D20" s="63" t="s">
+      <c r="B22" s="62" t="s">
+        <v>294</v>
+      </c>
+      <c r="C22" s="62" t="s">
+        <v>295</v>
+      </c>
+      <c r="D22" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="63" t="s">
-        <v>290</v>
-      </c>
-      <c r="F20" s="63" t="s">
-        <v>291</v>
-      </c>
-      <c r="G20" s="63" t="s">
-        <v>291</v>
-      </c>
-      <c r="H20" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20"/>
-    </row>
-    <row r="21" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A21" s="63" t="s">
+      <c r="E22" s="62" t="s">
+        <v>296</v>
+      </c>
+      <c r="F22" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="G22" s="62" t="s">
+        <v>298</v>
+      </c>
+      <c r="H22" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22"/>
+    </row>
+    <row r="23" spans="1:11" ht="84.6" thickBot="1">
+      <c r="A23" s="62" t="s">
         <v>316</v>
       </c>
-      <c r="B21" s="63" t="s">
-        <v>292</v>
-      </c>
-      <c r="C21" s="63" t="s">
-        <v>293</v>
-      </c>
-      <c r="D21" s="63" t="s">
+      <c r="B23" s="62" t="s">
+        <v>299</v>
+      </c>
+      <c r="C23" s="62" t="s">
+        <v>300</v>
+      </c>
+      <c r="D23" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="63" t="s">
-        <v>294</v>
-      </c>
-      <c r="F21" s="63" t="s">
-        <v>282</v>
-      </c>
-      <c r="G21" s="63" t="s">
-        <v>295</v>
-      </c>
-      <c r="H21" s="63" t="s">
-        <v>23</v>
-      </c>
-      <c r="K21"/>
-    </row>
-    <row r="22" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A22" s="63" t="s">
+      <c r="E23" s="62" t="s">
+        <v>301</v>
+      </c>
+      <c r="F23" s="62" t="s">
+        <v>302</v>
+      </c>
+      <c r="G23" s="62" t="s">
+        <v>303</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23"/>
+    </row>
+    <row r="24" spans="1:11" ht="67.8" thickBot="1">
+      <c r="A24" s="62" t="s">
         <v>317</v>
       </c>
-      <c r="B22" s="63" t="s">
-        <v>296</v>
-      </c>
-      <c r="C22" s="63" t="s">
-        <v>297</v>
-      </c>
-      <c r="D22" s="63" t="s">
+      <c r="B24" s="62" t="s">
+        <v>304</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="D24" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="63" t="s">
-        <v>298</v>
-      </c>
-      <c r="F22" s="63" t="s">
-        <v>299</v>
-      </c>
-      <c r="G22" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="H22" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22"/>
-    </row>
-    <row r="23" spans="1:11" ht="84.6" thickBot="1">
-      <c r="A23" s="63" t="s">
+      <c r="E24" s="62" t="s">
+        <v>305</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>306</v>
+      </c>
+      <c r="G24" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24"/>
+    </row>
+    <row r="25" spans="1:11" ht="67.8" thickBot="1">
+      <c r="A25" s="62" t="s">
         <v>318</v>
       </c>
-      <c r="B23" s="63" t="s">
-        <v>301</v>
-      </c>
-      <c r="C23" s="63" t="s">
-        <v>302</v>
-      </c>
-      <c r="D23" s="63" t="s">
+      <c r="B25" s="62" t="s">
+        <v>308</v>
+      </c>
+      <c r="C25" s="62" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="63" t="s">
-        <v>303</v>
-      </c>
-      <c r="F23" s="63" t="s">
-        <v>304</v>
-      </c>
-      <c r="G23" s="63" t="s">
-        <v>305</v>
-      </c>
-      <c r="H23" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23"/>
-    </row>
-    <row r="24" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A24" s="63" t="s">
-        <v>319</v>
-      </c>
-      <c r="B24" s="63" t="s">
-        <v>306</v>
-      </c>
-      <c r="C24" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="D24" s="63" t="s">
+      <c r="E25" s="62" t="s">
+        <v>309</v>
+      </c>
+      <c r="F25" s="62" t="s">
+        <v>310</v>
+      </c>
+      <c r="G25" s="62" t="s">
+        <v>311</v>
+      </c>
+      <c r="H25" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25"/>
+    </row>
+    <row r="26" spans="1:11" ht="67.8" thickBot="1">
+      <c r="A26" s="62" t="s">
+        <v>385</v>
+      </c>
+      <c r="B26" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="C26" s="62" t="s">
+        <v>382</v>
+      </c>
+      <c r="D26" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="63" t="s">
-        <v>307</v>
-      </c>
-      <c r="F24" s="63" t="s">
-        <v>308</v>
-      </c>
-      <c r="G24" s="63" t="s">
-        <v>309</v>
-      </c>
-      <c r="H24" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24"/>
-    </row>
-    <row r="25" spans="1:11" ht="67.8" thickBot="1">
-      <c r="A25" s="63" t="s">
-        <v>320</v>
-      </c>
-      <c r="B25" s="63" t="s">
-        <v>310</v>
-      </c>
-      <c r="C25" s="63" t="s">
-        <v>196</v>
-      </c>
-      <c r="D25" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="63" t="s">
-        <v>311</v>
-      </c>
-      <c r="F25" s="63" t="s">
-        <v>312</v>
-      </c>
-      <c r="G25" s="63" t="s">
-        <v>313</v>
-      </c>
-      <c r="H25" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25"/>
-    </row>
-    <row r="26" spans="1:11" ht="17.399999999999999">
-      <c r="A26" s="62"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
+      <c r="E26" s="62" t="s">
+        <v>384</v>
+      </c>
+      <c r="F26" s="62" t="s">
+        <v>383</v>
+      </c>
+      <c r="G26" s="62" t="s">
+        <v>383</v>
+      </c>
+      <c r="H26" s="62" t="s">
+        <v>21</v>
+      </c>
       <c r="K26"/>
     </row>
     <row r="27" spans="1:11">
@@ -3061,10 +3215,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="E1" s="72" t="s">
+      <c r="E1" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="73"/>
+      <c r="F1" s="77"/>
       <c r="G1" s="29" t="s">
         <v>2</v>
       </c>
@@ -3073,10 +3227,10 @@
       <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="73"/>
+      <c r="F2" s="77"/>
       <c r="G2" s="29" t="s">
         <v>24</v>
       </c>
@@ -3085,10 +3239,10 @@
       <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="E3" s="72" t="s">
+      <c r="E3" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="73"/>
+      <c r="F3" s="77"/>
       <c r="G3" s="35">
         <v>45516</v>
       </c>
@@ -3097,10 +3251,10 @@
       <c r="J3" s="38"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="E4" s="72" t="s">
+      <c r="E4" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="73"/>
+      <c r="F4" s="77"/>
       <c r="G4" s="35">
         <v>41985</v>
       </c>
@@ -3109,10 +3263,10 @@
       <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="E5" s="72" t="s">
+      <c r="E5" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="73"/>
+      <c r="F5" s="77"/>
       <c r="G5" s="29"/>
       <c r="I5" s="33"/>
       <c r="J5" s="34"/>
@@ -3676,52 +3830,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="74"/>
+      <c r="E1" s="78"/>
       <c r="F1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="75"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="D2" s="74" t="s">
+      <c r="D2" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="74"/>
+      <c r="E2" s="78"/>
       <c r="F2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="75"/>
+      <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="D3" s="74" t="s">
+      <c r="D3" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="74"/>
+      <c r="E3" s="78"/>
       <c r="F3" s="15">
         <v>45516</v>
       </c>
-      <c r="G3" s="76"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="D4" s="74" t="s">
+      <c r="D4" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="74"/>
+      <c r="E4" s="78"/>
       <c r="F4" s="15">
         <v>41985</v>
       </c>
-      <c r="G4" s="76"/>
+      <c r="G4" s="67"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="D5" s="74" t="s">
+      <c r="D5" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="74"/>
+      <c r="E5" s="78"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="75"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:10">
       <c r="D6" s="7"/>
@@ -3753,9 +3907,8 @@
       <c r="F8" s="1">
         <v>0</v>
       </c>
-      <c r="G8" s="77"/>
-    </row>
-    <row r="9" spans="1:10">
+    </row>
+    <row r="9" spans="1:10" ht="20.399999999999999">
       <c r="A9" s="12" t="s">
         <v>11</v>
       </c>
@@ -3763,13 +3916,13 @@
         <v>31</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>340</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>342</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>29</v>
@@ -4061,7 +4214,7 @@
         <v>104</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F20" s="46" t="s">
         <v>153</v>
@@ -4075,25 +4228,25 @@
     </row>
     <row r="21" spans="1:8" ht="28.2">
       <c r="A21" s="46" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D21" s="46" t="s">
         <v>104</v>
       </c>
       <c r="E21" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="F21" s="47" t="s">
+        <v>325</v>
+      </c>
+      <c r="G21" s="47" t="s">
         <v>326</v>
-      </c>
-      <c r="F21" s="47" t="s">
-        <v>327</v>
-      </c>
-      <c r="G21" s="47" t="s">
-        <v>328</v>
       </c>
       <c r="H21" s="46" t="s">
         <v>21</v>
@@ -4188,7 +4341,7 @@
         <v>9</v>
       </c>
       <c r="E7" s="41">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="41"/>
     </row>
@@ -4197,7 +4350,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="57" customFormat="1" ht="28.2" thickBot="1">
@@ -4473,13 +4626,13 @@
         <v>221</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F20" s="58" t="s">
         <v>344</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="99" customHeight="1" thickBot="1">
@@ -4496,13 +4649,13 @@
         <v>224</v>
       </c>
       <c r="E21" s="58" t="s">
-        <v>225</v>
+        <v>345</v>
       </c>
       <c r="F21" s="58" t="s">
         <v>225</v>
       </c>
       <c r="G21" s="59" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="71.400000000000006" customHeight="1" thickBot="1">
@@ -4732,6 +4885,339 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407BF401-235A-4B80-82D4-2E02A2B9E0B2}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="30.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F1" t="s">
+        <v>351</v>
+      </c>
+      <c r="G1" t="s">
+        <v>352</v>
+      </c>
+      <c r="H1" t="s">
+        <v>353</v>
+      </c>
+      <c r="I1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F2" s="68" t="s">
+        <v>359</v>
+      </c>
+      <c r="G2" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" t="s">
+        <v>357</v>
+      </c>
+      <c r="E3" t="s">
+        <v>358</v>
+      </c>
+      <c r="F3" s="68" t="s">
+        <v>365</v>
+      </c>
+      <c r="G3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H3" t="s">
+        <v>361</v>
+      </c>
+      <c r="I3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D4" t="s">
+        <v>364</v>
+      </c>
+      <c r="F4" s="68" t="s">
+        <v>366</v>
+      </c>
+      <c r="G4" t="s">
+        <v>360</v>
+      </c>
+      <c r="H4" t="s">
+        <v>361</v>
+      </c>
+      <c r="I4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D5" t="s">
+        <v>364</v>
+      </c>
+      <c r="E5" t="s">
+        <v>358</v>
+      </c>
+      <c r="F5" s="68"/>
+      <c r="G5" t="s">
+        <v>360</v>
+      </c>
+      <c r="H5" t="s">
+        <v>361</v>
+      </c>
+      <c r="I5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F6" s="68" t="s">
+        <v>367</v>
+      </c>
+      <c r="H6" t="s">
+        <v>361</v>
+      </c>
+      <c r="I6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B7" t="s">
+        <v>356</v>
+      </c>
+      <c r="C7" t="s">
+        <v>357</v>
+      </c>
+      <c r="D7" t="s">
+        <v>364</v>
+      </c>
+      <c r="E7" t="s">
+        <v>358</v>
+      </c>
+      <c r="F7" s="68" t="s">
+        <v>368</v>
+      </c>
+      <c r="G7" t="s">
+        <v>360</v>
+      </c>
+      <c r="I7" s="70" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="10" customFormat="1" ht="34.200000000000003" customHeight="1">
+      <c r="A8" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F8" s="71" t="s">
+        <v>369</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>355</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>357</v>
+      </c>
+      <c r="D9" t="s">
+        <v>364</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F9" s="71" t="s">
+        <v>369</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="I9" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>355</v>
+      </c>
+      <c r="B10" t="s">
+        <v>356</v>
+      </c>
+      <c r="C10" t="s">
+        <v>357</v>
+      </c>
+      <c r="D10" t="s">
+        <v>364</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F10" s="71" t="s">
+        <v>377</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="I10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>355</v>
+      </c>
+      <c r="B11" t="s">
+        <v>356</v>
+      </c>
+      <c r="C11" t="s">
+        <v>357</v>
+      </c>
+      <c r="D11" t="s">
+        <v>364</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F11" s="71" t="s">
+        <v>377</v>
+      </c>
+      <c r="G11" t="s">
+        <v>379</v>
+      </c>
+      <c r="I11" s="70" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B12" t="s">
+        <v>356</v>
+      </c>
+      <c r="C12" t="s">
+        <v>357</v>
+      </c>
+      <c r="D12" t="s">
+        <v>364</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F12">
+        <v>2122</v>
+      </c>
+      <c r="G12" t="s">
+        <v>380</v>
+      </c>
+      <c r="I12" s="70" t="s">
+        <v>373</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{B5D9ABFE-A300-4437-A125-B1E52D1C34F4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E0F943-41AD-463A-9AD1-A9D21A7C73EE}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4744,20 +5230,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="63" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1" s="64" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1" s="64" t="s">
         <v>331</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="D1" s="64" t="s">
         <v>332</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>333</v>
-      </c>
-      <c r="D1" s="65" t="s">
-        <v>334</v>
-      </c>
-      <c r="E1" s="65" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4765,13 +5251,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -4782,7 +5268,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C3">
         <v>11</v>
@@ -4799,7 +5285,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C4">
         <v>12</v>
@@ -4816,26 +5302,26 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C5">
         <v>21</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="C6">
         <v>58</v>
       </c>
-      <c r="D6" s="67">
+      <c r="D6" s="66">
         <v>56</v>
       </c>
-      <c r="E6" s="66">
+      <c r="E6" s="65">
         <v>2</v>
       </c>
     </row>
